--- a/02 Solution Architecture/design/Features.xlsx
+++ b/02 Solution Architecture/design/Features.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sougatabagchi/Projects/MSIL/work2/design/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sougatabagchi/Projects/MSIL/Enterprise-PM-Platform/epms-2/02 Solution Architecture/design/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA6A33FD-BDA7-3347-80A7-238805183382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50B6AA2F-A455-7A4A-971D-7F0510203228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{5C9540A5-4EF1-0A4E-8E67-4A8A83FA1D22}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="1" xr2:uid="{5C9540A5-4EF1-0A4E-8E67-4A8A83FA1D22}"/>
   </bookViews>
   <sheets>
     <sheet name="Campaign" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="262">
   <si>
     <t>Features</t>
   </si>
@@ -114,14 +115,737 @@
   </si>
   <si>
     <t>View Campagn Detail UI Feields</t>
+  </si>
+  <si>
+    <t>Entity</t>
+  </si>
+  <si>
+    <t>Attribute</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>PK/FK</t>
+  </si>
+  <si>
+    <t>Mandatory</t>
+  </si>
+  <si>
+    <t>Demand</t>
+  </si>
+  <si>
+    <t>demand_id</t>
+  </si>
+  <si>
+    <t>VARCHAR(20)</t>
+  </si>
+  <si>
+    <t>PK</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Unique identifier for demand</t>
+  </si>
+  <si>
+    <t>demand_title</t>
+  </si>
+  <si>
+    <t>VARCHAR(255)</t>
+  </si>
+  <si>
+    <t>Title of the demand</t>
+  </si>
+  <si>
+    <t>demand_description</t>
+  </si>
+  <si>
+    <t>TEXT</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Description of demand</t>
+  </si>
+  <si>
+    <t>division_id</t>
+  </si>
+  <si>
+    <t>FK</t>
+  </si>
+  <si>
+    <t>coe_id</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>VARCHAR(30)</t>
+  </si>
+  <si>
+    <t>Demand status</t>
+  </si>
+  <si>
+    <t>created_by</t>
+  </si>
+  <si>
+    <t>VARCHAR(50)</t>
+  </si>
+  <si>
+    <t>User who created demand</t>
+  </si>
+  <si>
+    <t>created_at</t>
+  </si>
+  <si>
+    <t>TIMESTAMP</t>
+  </si>
+  <si>
+    <t>Demand creation timestamp</t>
+  </si>
+  <si>
+    <t>Program</t>
+  </si>
+  <si>
+    <t>program_id</t>
+  </si>
+  <si>
+    <t>Unique identifier for program</t>
+  </si>
+  <si>
+    <t>program_name</t>
+  </si>
+  <si>
+    <t>Program name</t>
+  </si>
+  <si>
+    <t>program_description</t>
+  </si>
+  <si>
+    <t>Description of program</t>
+  </si>
+  <si>
+    <t>Division owning the program</t>
+  </si>
+  <si>
+    <t>CoE responsible for program</t>
+  </si>
+  <si>
+    <t>Program status</t>
+  </si>
+  <si>
+    <t>User who created program</t>
+  </si>
+  <si>
+    <t>Program creation timestamp</t>
+  </si>
+  <si>
+    <t>Project</t>
+  </si>
+  <si>
+    <t>project_id</t>
+  </si>
+  <si>
+    <t>Unique project identifier</t>
+  </si>
+  <si>
+    <t>Demand from which project is created</t>
+  </si>
+  <si>
+    <t>Program associated with project</t>
+  </si>
+  <si>
+    <t>project_name</t>
+  </si>
+  <si>
+    <t>Project name</t>
+  </si>
+  <si>
+    <t>project_type</t>
+  </si>
+  <si>
+    <t>Project type (POC, etc.)</t>
+  </si>
+  <si>
+    <t>expected_start_date</t>
+  </si>
+  <si>
+    <t>DATE</t>
+  </si>
+  <si>
+    <t>Expected project start date</t>
+  </si>
+  <si>
+    <t>expected_end_date</t>
+  </si>
+  <si>
+    <t>Expected project end date</t>
+  </si>
+  <si>
+    <t>budget_amount</t>
+  </si>
+  <si>
+    <t>DECIMAL(15,2)</t>
+  </si>
+  <si>
+    <t>Budget allocated for project</t>
+  </si>
+  <si>
+    <t>budget_currency</t>
+  </si>
+  <si>
+    <t>VARCHAR(10)</t>
+  </si>
+  <si>
+    <t>Currency for project budget</t>
+  </si>
+  <si>
+    <t>Current project status</t>
+  </si>
+  <si>
+    <t>BOOLEAN</t>
+  </si>
+  <si>
+    <t>User who created project</t>
+  </si>
+  <si>
+    <t>Project creation timestamp</t>
+  </si>
+  <si>
+    <t>updated_at</t>
+  </si>
+  <si>
+    <t>Last update timestamp</t>
+  </si>
+  <si>
+    <t>VCF</t>
+  </si>
+  <si>
+    <t>vcf_id</t>
+  </si>
+  <si>
+    <t>Unique identifier for VCF record</t>
+  </si>
+  <si>
+    <t>Program associated with VCF</t>
+  </si>
+  <si>
+    <t>version_no</t>
+  </si>
+  <si>
+    <t>Version number of VCF</t>
+  </si>
+  <si>
+    <t>vcf_status</t>
+  </si>
+  <si>
+    <t>Status of VCF</t>
+  </si>
+  <si>
+    <t>effective_from</t>
+  </si>
+  <si>
+    <t>Start date of VCF validity</t>
+  </si>
+  <si>
+    <t>effective_to</t>
+  </si>
+  <si>
+    <t>End date of VCF validity</t>
+  </si>
+  <si>
+    <t>updated_by</t>
+  </si>
+  <si>
+    <t>User who updated VCF</t>
+  </si>
+  <si>
+    <t>Timestamp of VCF update</t>
+  </si>
+  <si>
+    <t>Manpower_Estimate</t>
+  </si>
+  <si>
+    <t>manpower_estimate_id</t>
+  </si>
+  <si>
+    <t>Unique manpower estimate record</t>
+  </si>
+  <si>
+    <t>Project associated with manpower estimate</t>
+  </si>
+  <si>
+    <t>skillset</t>
+  </si>
+  <si>
+    <t>VARCHAR(100)</t>
+  </si>
+  <si>
+    <t>Skillset required</t>
+  </si>
+  <si>
+    <t>headcount</t>
+  </si>
+  <si>
+    <t>INT</t>
+  </si>
+  <si>
+    <t>Number of resources required</t>
+  </si>
+  <si>
+    <t>utilization_percentage</t>
+  </si>
+  <si>
+    <t>DECIMAL(5,2)</t>
+  </si>
+  <si>
+    <t>Utilization percentage</t>
+  </si>
+  <si>
+    <t>start_date</t>
+  </si>
+  <si>
+    <t>Resource start date</t>
+  </si>
+  <si>
+    <t>end_date</t>
+  </si>
+  <si>
+    <t>Resource end date</t>
+  </si>
+  <si>
+    <t>remarks</t>
+  </si>
+  <si>
+    <t>Additional comments</t>
+  </si>
+  <si>
+    <t>Creation timestamp</t>
+  </si>
+  <si>
+    <t>Division</t>
+  </si>
+  <si>
+    <t>Unique division identifier</t>
+  </si>
+  <si>
+    <t>division_name</t>
+  </si>
+  <si>
+    <t>Division name</t>
+  </si>
+  <si>
+    <t>division_code</t>
+  </si>
+  <si>
+    <t>Division code</t>
+  </si>
+  <si>
+    <t>CoE</t>
+  </si>
+  <si>
+    <t>Unique CoE identifier</t>
+  </si>
+  <si>
+    <t>coe_name</t>
+  </si>
+  <si>
+    <t>Name of Center of Excellence</t>
+  </si>
+  <si>
+    <t>coe_code</t>
+  </si>
+  <si>
+    <t>CoE code</t>
+  </si>
+  <si>
+    <t>User</t>
+  </si>
+  <si>
+    <t>user_id</t>
+  </si>
+  <si>
+    <t>Unique user identifier</t>
+  </si>
+  <si>
+    <t>employee_no</t>
+  </si>
+  <si>
+    <t>Employee number</t>
+  </si>
+  <si>
+    <t>user_name</t>
+  </si>
+  <si>
+    <t>Full name of user</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>VARCHAR(150)</t>
+  </si>
+  <si>
+    <t>User email address</t>
+  </si>
+  <si>
+    <t>role</t>
+  </si>
+  <si>
+    <t>Role (Business Partner, Governance Head, etc.)</t>
+  </si>
+  <si>
+    <t>User account status</t>
+  </si>
+  <si>
+    <t>Project_Approval</t>
+  </si>
+  <si>
+    <t>approval_id</t>
+  </si>
+  <si>
+    <t>Unique approval record</t>
+  </si>
+  <si>
+    <t>Project being approved</t>
+  </si>
+  <si>
+    <t>approver_user_id</t>
+  </si>
+  <si>
+    <t>User performing approval</t>
+  </si>
+  <si>
+    <t>approver_role</t>
+  </si>
+  <si>
+    <t>Role of approver</t>
+  </si>
+  <si>
+    <t>approval_stage</t>
+  </si>
+  <si>
+    <t>Stage in approval workflow</t>
+  </si>
+  <si>
+    <t>approval_status</t>
+  </si>
+  <si>
+    <t>Approved / Rejected / Pending</t>
+  </si>
+  <si>
+    <t>comments</t>
+  </si>
+  <si>
+    <t>Comments from approver</t>
+  </si>
+  <si>
+    <t>action_at</t>
+  </si>
+  <si>
+    <t>Timestamp of approval action</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill </t>
+  </si>
+  <si>
+    <t>Fk</t>
+  </si>
+  <si>
+    <t>Unique identifier for the program</t>
+  </si>
+  <si>
+    <t>Demand ID from which the program is created (auto populated, non-editable)</t>
+  </si>
+  <si>
+    <t>Name of the program</t>
+  </si>
+  <si>
+    <t>Detailed description of the program</t>
+  </si>
+  <si>
+    <t>program_start_year</t>
+  </si>
+  <si>
+    <t>YEAR / INT</t>
+  </si>
+  <si>
+    <t>Year in which the program starts</t>
+  </si>
+  <si>
+    <t>program_type</t>
+  </si>
+  <si>
+    <t>Type of program (Software / Non-Software)</t>
+  </si>
+  <si>
+    <t>ownership_type</t>
+  </si>
+  <si>
+    <t>Ownership of program (Business / DE)</t>
+  </si>
+  <si>
+    <t>business_spoc_id</t>
+  </si>
+  <si>
+    <t>Employee ID of Business SPOC selected from HRMS</t>
+  </si>
+  <si>
+    <t>business_vertical</t>
+  </si>
+  <si>
+    <t>Business vertical auto-populated based on selected employee</t>
+  </si>
+  <si>
+    <t>investment_category</t>
+  </si>
+  <si>
+    <t>Investment category (Mega / High / Medium / Low)</t>
+  </si>
+  <si>
+    <t>program_classification</t>
+  </si>
+  <si>
+    <t>Classification of program (Enterprise Transformation / Efficiency Tool / Essential / Established Technologies / Experimental)</t>
+  </si>
+  <si>
+    <t>User who created the program</t>
+  </si>
+  <si>
+    <t>Last user who updated program</t>
+  </si>
+  <si>
+    <t>Program_DE_Pillar</t>
+  </si>
+  <si>
+    <t>program_de_pillar_id</t>
+  </si>
+  <si>
+    <t>Unique record identifier</t>
+  </si>
+  <si>
+    <t>Program to which DE pillar is associated</t>
+  </si>
+  <si>
+    <t>de_pillar</t>
+  </si>
+  <si>
+    <t>CHAR(1)</t>
+  </si>
+  <si>
+    <t>DE pillar value (A / B / C / D / E)</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>DE Pillar ID</t>
+  </si>
+  <si>
+    <t>Unique identifier for the VCF record</t>
+  </si>
+  <si>
+    <t>Program ID to which this VCF belongs</t>
+  </si>
+  <si>
+    <t>Version number of the VCF for a program</t>
+  </si>
+  <si>
+    <t>vcf_name</t>
+  </si>
+  <si>
+    <t>Optional name/title of the VCF</t>
+  </si>
+  <si>
+    <t>Status of VCF (Draft / Submitted / Approved / Archived)</t>
+  </si>
+  <si>
+    <t>Starting financial/planning year for the VCF</t>
+  </si>
+  <si>
+    <t>npv</t>
+  </si>
+  <si>
+    <t>DECIMAL(18,2)</t>
+  </si>
+  <si>
+    <t>Net Present Value derived from VCF framework</t>
+  </si>
+  <si>
+    <t>irr</t>
+  </si>
+  <si>
+    <t>DECIMAL(7,2)</t>
+  </si>
+  <si>
+    <t>Internal Rate of Return derived from VCF framework</t>
+  </si>
+  <si>
+    <t>User who created the VCF version</t>
+  </si>
+  <si>
+    <t>User who last updated the VCF</t>
+  </si>
+  <si>
+    <t>VARCHAR(500)</t>
+  </si>
+  <si>
+    <t>General remarks/comments for the VCF</t>
+  </si>
+  <si>
+    <t>VCF_Value_Lever</t>
+  </si>
+  <si>
+    <t>value_lever_id</t>
+  </si>
+  <si>
+    <t>Unique identifier for a value lever</t>
+  </si>
+  <si>
+    <t>VCF to which the value lever belongs</t>
+  </si>
+  <si>
+    <t>lever_name</t>
+  </si>
+  <si>
+    <t>Name of the value lever</t>
+  </si>
+  <si>
+    <t>display_order</t>
+  </si>
+  <si>
+    <t>Sequence/order in which the lever is shown</t>
+  </si>
+  <si>
+    <t>is_active</t>
+  </si>
+  <si>
+    <t>Indicates whether the lever is active in this version</t>
+  </si>
+  <si>
+    <t>VCF_Value_Lever_Year</t>
+  </si>
+  <si>
+    <t>value_lever_year_id</t>
+  </si>
+  <si>
+    <t>Unique identifier for yearly value lever data</t>
+  </si>
+  <si>
+    <t>Value lever to which this yearly value belongs</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>Planning/reporting year</t>
+  </si>
+  <si>
+    <t>amount</t>
+  </si>
+  <si>
+    <t>Year-wise amount/value for the lever</t>
+  </si>
+  <si>
+    <t>currency</t>
+  </si>
+  <si>
+    <t>Currency for the amount</t>
+  </si>
+  <si>
+    <t>VCF_Cost_Lever</t>
+  </si>
+  <si>
+    <t>cost_lever_id</t>
+  </si>
+  <si>
+    <t>Unique identifier for a cost lever</t>
+  </si>
+  <si>
+    <t>VCF to which the cost lever belongs</t>
+  </si>
+  <si>
+    <t>Name of the cost lever</t>
+  </si>
+  <si>
+    <t>Indicates whether the cost lever is active in this version</t>
+  </si>
+  <si>
+    <t>VCF_Version_History</t>
+  </si>
+  <si>
+    <t>history_id</t>
+  </si>
+  <si>
+    <t>Unique identifier for version history record</t>
+  </si>
+  <si>
+    <t>VCF record</t>
+  </si>
+  <si>
+    <t>Version number</t>
+  </si>
+  <si>
+    <t>change_summary</t>
+  </si>
+  <si>
+    <t>Summary of changes made in this version</t>
+  </si>
+  <si>
+    <t>changed_by</t>
+  </si>
+  <si>
+    <t>User who made the change</t>
+  </si>
+  <si>
+    <t>changed_at</t>
+  </si>
+  <si>
+    <t>Timestamp of change</t>
+  </si>
+  <si>
+    <t>VCF_Cost_Lever_Year</t>
+  </si>
+  <si>
+    <t>cost_lever_year_id</t>
+  </si>
+  <si>
+    <t>Unique identifier for yearly cost lever data</t>
+  </si>
+  <si>
+    <t>Cost lever to which this yearly value belongs</t>
+  </si>
+  <si>
+    <t>Year-wise amount/cost for the lever</t>
+  </si>
+  <si>
+    <t>effective_year</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -149,8 +873,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -676,4 +1402,2563 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F44B1572-BEE2-BB4B-899C-63B0B6177E9E}">
+  <dimension ref="B2:G163"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.83203125" customWidth="1"/>
+    <col min="7" max="7" width="35" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" t="s">
+        <v>69</v>
+      </c>
+      <c r="D20" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" t="s">
+        <v>34</v>
+      </c>
+      <c r="F20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G20" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" t="s">
+        <v>33</v>
+      </c>
+      <c r="E21" t="s">
+        <v>45</v>
+      </c>
+      <c r="F21" t="s">
+        <v>35</v>
+      </c>
+      <c r="G21" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" t="s">
+        <v>45</v>
+      </c>
+      <c r="F22" t="s">
+        <v>42</v>
+      </c>
+      <c r="G22" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B23" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" t="s">
+        <v>73</v>
+      </c>
+      <c r="D23" t="s">
+        <v>38</v>
+      </c>
+      <c r="F23" t="s">
+        <v>35</v>
+      </c>
+      <c r="G23" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B24" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D24" t="s">
+        <v>51</v>
+      </c>
+      <c r="F24" t="s">
+        <v>35</v>
+      </c>
+      <c r="G24" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B25" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25" t="s">
+        <v>77</v>
+      </c>
+      <c r="D25" t="s">
+        <v>78</v>
+      </c>
+      <c r="F25" t="s">
+        <v>35</v>
+      </c>
+      <c r="G25" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B26" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" t="s">
+        <v>78</v>
+      </c>
+      <c r="F26" t="s">
+        <v>35</v>
+      </c>
+      <c r="G26" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B27" t="s">
+        <v>68</v>
+      </c>
+      <c r="C27" t="s">
+        <v>82</v>
+      </c>
+      <c r="D27" t="s">
+        <v>83</v>
+      </c>
+      <c r="F27" t="s">
+        <v>42</v>
+      </c>
+      <c r="G27" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C28" t="s">
+        <v>85</v>
+      </c>
+      <c r="D28" t="s">
+        <v>86</v>
+      </c>
+      <c r="F28" t="s">
+        <v>42</v>
+      </c>
+      <c r="G28" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B29" t="s">
+        <v>68</v>
+      </c>
+      <c r="C29" t="s">
+        <v>47</v>
+      </c>
+      <c r="D29" t="s">
+        <v>48</v>
+      </c>
+      <c r="F29" t="s">
+        <v>35</v>
+      </c>
+      <c r="G29" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B30" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" t="s">
+        <v>110</v>
+      </c>
+      <c r="D30" t="s">
+        <v>33</v>
+      </c>
+      <c r="E30" t="s">
+        <v>171</v>
+      </c>
+      <c r="F30" t="s">
+        <v>35</v>
+      </c>
+      <c r="G30" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B31" t="s">
+        <v>68</v>
+      </c>
+      <c r="C31" t="s">
+        <v>50</v>
+      </c>
+      <c r="D31" t="s">
+        <v>51</v>
+      </c>
+      <c r="E31" t="s">
+        <v>45</v>
+      </c>
+      <c r="F31" t="s">
+        <v>35</v>
+      </c>
+      <c r="G31" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B32" t="s">
+        <v>68</v>
+      </c>
+      <c r="C32" t="s">
+        <v>53</v>
+      </c>
+      <c r="D32" t="s">
+        <v>54</v>
+      </c>
+      <c r="F32" t="s">
+        <v>35</v>
+      </c>
+      <c r="G32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B33" t="s">
+        <v>68</v>
+      </c>
+      <c r="C33" t="s">
+        <v>92</v>
+      </c>
+      <c r="D33" t="s">
+        <v>54</v>
+      </c>
+      <c r="F33" t="s">
+        <v>42</v>
+      </c>
+      <c r="G33" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B35" t="s">
+        <v>94</v>
+      </c>
+      <c r="C35" t="s">
+        <v>95</v>
+      </c>
+      <c r="D35" t="s">
+        <v>33</v>
+      </c>
+      <c r="E35" t="s">
+        <v>34</v>
+      </c>
+      <c r="F35" t="s">
+        <v>35</v>
+      </c>
+      <c r="G35" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B36" t="s">
+        <v>94</v>
+      </c>
+      <c r="C36" t="s">
+        <v>57</v>
+      </c>
+      <c r="D36" t="s">
+        <v>33</v>
+      </c>
+      <c r="E36" t="s">
+        <v>45</v>
+      </c>
+      <c r="F36" t="s">
+        <v>35</v>
+      </c>
+      <c r="G36" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B37" t="s">
+        <v>94</v>
+      </c>
+      <c r="C37" t="s">
+        <v>98</v>
+      </c>
+      <c r="D37" t="s">
+        <v>86</v>
+      </c>
+      <c r="F37" t="s">
+        <v>35</v>
+      </c>
+      <c r="G37" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B38" t="s">
+        <v>94</v>
+      </c>
+      <c r="C38" t="s">
+        <v>100</v>
+      </c>
+      <c r="D38" t="s">
+        <v>48</v>
+      </c>
+      <c r="F38" t="s">
+        <v>35</v>
+      </c>
+      <c r="G38" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B39" t="s">
+        <v>94</v>
+      </c>
+      <c r="C39" t="s">
+        <v>102</v>
+      </c>
+      <c r="D39" t="s">
+        <v>78</v>
+      </c>
+      <c r="F39" t="s">
+        <v>42</v>
+      </c>
+      <c r="G39" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B40" t="s">
+        <v>94</v>
+      </c>
+      <c r="C40" t="s">
+        <v>104</v>
+      </c>
+      <c r="D40" t="s">
+        <v>78</v>
+      </c>
+      <c r="F40" t="s">
+        <v>42</v>
+      </c>
+      <c r="G40" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B41" t="s">
+        <v>94</v>
+      </c>
+      <c r="C41" t="s">
+        <v>106</v>
+      </c>
+      <c r="D41" t="s">
+        <v>51</v>
+      </c>
+      <c r="E41" t="s">
+        <v>45</v>
+      </c>
+      <c r="F41" t="s">
+        <v>35</v>
+      </c>
+      <c r="G41" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B42" t="s">
+        <v>94</v>
+      </c>
+      <c r="C42" t="s">
+        <v>92</v>
+      </c>
+      <c r="D42" t="s">
+        <v>54</v>
+      </c>
+      <c r="E42" t="s">
+        <v>35</v>
+      </c>
+      <c r="F42" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B44" t="s">
+        <v>109</v>
+      </c>
+      <c r="C44" t="s">
+        <v>110</v>
+      </c>
+      <c r="D44" t="s">
+        <v>33</v>
+      </c>
+      <c r="E44" t="s">
+        <v>34</v>
+      </c>
+      <c r="F44" t="s">
+        <v>35</v>
+      </c>
+      <c r="G44" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B45" t="s">
+        <v>109</v>
+      </c>
+      <c r="C45" t="s">
+        <v>69</v>
+      </c>
+      <c r="D45" t="s">
+        <v>33</v>
+      </c>
+      <c r="E45" t="s">
+        <v>45</v>
+      </c>
+      <c r="F45" t="s">
+        <v>35</v>
+      </c>
+      <c r="G45" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B46" t="s">
+        <v>109</v>
+      </c>
+      <c r="C46" t="s">
+        <v>113</v>
+      </c>
+      <c r="D46" t="s">
+        <v>114</v>
+      </c>
+      <c r="F46" t="s">
+        <v>35</v>
+      </c>
+      <c r="G46" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B47" t="s">
+        <v>109</v>
+      </c>
+      <c r="C47" t="s">
+        <v>116</v>
+      </c>
+      <c r="D47" t="s">
+        <v>117</v>
+      </c>
+      <c r="F47" t="s">
+        <v>35</v>
+      </c>
+      <c r="G47" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B48" t="s">
+        <v>109</v>
+      </c>
+      <c r="C48" t="s">
+        <v>119</v>
+      </c>
+      <c r="D48" t="s">
+        <v>120</v>
+      </c>
+      <c r="F48" t="s">
+        <v>35</v>
+      </c>
+      <c r="G48" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B49" t="s">
+        <v>109</v>
+      </c>
+      <c r="C49" t="s">
+        <v>122</v>
+      </c>
+      <c r="D49" t="s">
+        <v>78</v>
+      </c>
+      <c r="F49" t="s">
+        <v>35</v>
+      </c>
+      <c r="G49" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B50" t="s">
+        <v>109</v>
+      </c>
+      <c r="C50" t="s">
+        <v>124</v>
+      </c>
+      <c r="D50" t="s">
+        <v>78</v>
+      </c>
+      <c r="F50" t="s">
+        <v>35</v>
+      </c>
+      <c r="G50" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B51" t="s">
+        <v>109</v>
+      </c>
+      <c r="C51" t="s">
+        <v>126</v>
+      </c>
+      <c r="D51" t="s">
+        <v>38</v>
+      </c>
+      <c r="F51" t="s">
+        <v>42</v>
+      </c>
+      <c r="G51" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B52" t="s">
+        <v>109</v>
+      </c>
+      <c r="C52" t="s">
+        <v>53</v>
+      </c>
+      <c r="D52" t="s">
+        <v>54</v>
+      </c>
+      <c r="F52" t="s">
+        <v>35</v>
+      </c>
+      <c r="G52" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="54" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B54" t="s">
+        <v>129</v>
+      </c>
+      <c r="C54" t="s">
+        <v>44</v>
+      </c>
+      <c r="D54" t="s">
+        <v>33</v>
+      </c>
+      <c r="E54" t="s">
+        <v>34</v>
+      </c>
+      <c r="F54" t="s">
+        <v>35</v>
+      </c>
+      <c r="G54" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B55" t="s">
+        <v>129</v>
+      </c>
+      <c r="C55" t="s">
+        <v>131</v>
+      </c>
+      <c r="D55" t="s">
+        <v>114</v>
+      </c>
+      <c r="F55" t="s">
+        <v>35</v>
+      </c>
+      <c r="G55" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="56" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B56" t="s">
+        <v>129</v>
+      </c>
+      <c r="C56" t="s">
+        <v>133</v>
+      </c>
+      <c r="D56" t="s">
+        <v>33</v>
+      </c>
+      <c r="F56" t="s">
+        <v>35</v>
+      </c>
+      <c r="G56" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="58" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B58" t="s">
+        <v>135</v>
+      </c>
+      <c r="C58" t="s">
+        <v>46</v>
+      </c>
+      <c r="D58" t="s">
+        <v>33</v>
+      </c>
+      <c r="E58" t="s">
+        <v>34</v>
+      </c>
+      <c r="F58" t="s">
+        <v>35</v>
+      </c>
+      <c r="G58" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="59" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B59" t="s">
+        <v>135</v>
+      </c>
+      <c r="C59" t="s">
+        <v>137</v>
+      </c>
+      <c r="D59" t="s">
+        <v>114</v>
+      </c>
+      <c r="F59" t="s">
+        <v>35</v>
+      </c>
+      <c r="G59" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="60" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B60" t="s">
+        <v>135</v>
+      </c>
+      <c r="C60" t="s">
+        <v>139</v>
+      </c>
+      <c r="D60" t="s">
+        <v>33</v>
+      </c>
+      <c r="F60" t="s">
+        <v>35</v>
+      </c>
+      <c r="G60" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="61" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B61" t="s">
+        <v>141</v>
+      </c>
+      <c r="C61" t="s">
+        <v>142</v>
+      </c>
+      <c r="D61" t="s">
+        <v>51</v>
+      </c>
+      <c r="E61" t="s">
+        <v>34</v>
+      </c>
+      <c r="F61" t="s">
+        <v>35</v>
+      </c>
+      <c r="G61" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="62" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B62" t="s">
+        <v>141</v>
+      </c>
+      <c r="C62" t="s">
+        <v>144</v>
+      </c>
+      <c r="D62" t="s">
+        <v>33</v>
+      </c>
+      <c r="F62" t="s">
+        <v>35</v>
+      </c>
+      <c r="G62" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="63" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B63" t="s">
+        <v>141</v>
+      </c>
+      <c r="C63" t="s">
+        <v>146</v>
+      </c>
+      <c r="D63" t="s">
+        <v>114</v>
+      </c>
+      <c r="F63" t="s">
+        <v>35</v>
+      </c>
+      <c r="G63" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="64" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B64" t="s">
+        <v>141</v>
+      </c>
+      <c r="C64" t="s">
+        <v>148</v>
+      </c>
+      <c r="D64" t="s">
+        <v>149</v>
+      </c>
+      <c r="F64" t="s">
+        <v>35</v>
+      </c>
+      <c r="G64" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="65" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B65" t="s">
+        <v>141</v>
+      </c>
+      <c r="C65" t="s">
+        <v>151</v>
+      </c>
+      <c r="D65" t="s">
+        <v>51</v>
+      </c>
+      <c r="F65" t="s">
+        <v>35</v>
+      </c>
+      <c r="G65" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="66" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B66" t="s">
+        <v>141</v>
+      </c>
+      <c r="C66" t="s">
+        <v>47</v>
+      </c>
+      <c r="D66" t="s">
+        <v>33</v>
+      </c>
+      <c r="F66" t="s">
+        <v>35</v>
+      </c>
+      <c r="G66" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="68" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B68" t="s">
+        <v>154</v>
+      </c>
+      <c r="C68" t="s">
+        <v>155</v>
+      </c>
+      <c r="D68" t="s">
+        <v>33</v>
+      </c>
+      <c r="E68" t="s">
+        <v>34</v>
+      </c>
+      <c r="F68" t="s">
+        <v>35</v>
+      </c>
+      <c r="G68" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="69" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B69" t="s">
+        <v>154</v>
+      </c>
+      <c r="C69" t="s">
+        <v>69</v>
+      </c>
+      <c r="D69" t="s">
+        <v>33</v>
+      </c>
+      <c r="E69" t="s">
+        <v>45</v>
+      </c>
+      <c r="F69" t="s">
+        <v>35</v>
+      </c>
+      <c r="G69" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="70" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B70" t="s">
+        <v>154</v>
+      </c>
+      <c r="C70" t="s">
+        <v>158</v>
+      </c>
+      <c r="D70" t="s">
+        <v>51</v>
+      </c>
+      <c r="E70" t="s">
+        <v>45</v>
+      </c>
+      <c r="F70" t="s">
+        <v>35</v>
+      </c>
+      <c r="G70" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="71" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B71" t="s">
+        <v>154</v>
+      </c>
+      <c r="C71" t="s">
+        <v>160</v>
+      </c>
+      <c r="D71" t="s">
+        <v>51</v>
+      </c>
+      <c r="F71" t="s">
+        <v>35</v>
+      </c>
+      <c r="G71" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="72" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B72" t="s">
+        <v>154</v>
+      </c>
+      <c r="C72" t="s">
+        <v>162</v>
+      </c>
+      <c r="D72" t="s">
+        <v>51</v>
+      </c>
+      <c r="F72" t="s">
+        <v>35</v>
+      </c>
+      <c r="G72" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="73" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B73" t="s">
+        <v>154</v>
+      </c>
+      <c r="C73" t="s">
+        <v>164</v>
+      </c>
+      <c r="D73" t="s">
+        <v>48</v>
+      </c>
+      <c r="F73" t="s">
+        <v>35</v>
+      </c>
+      <c r="G73" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="74" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B74" t="s">
+        <v>154</v>
+      </c>
+      <c r="C74" t="s">
+        <v>166</v>
+      </c>
+      <c r="D74" t="s">
+        <v>38</v>
+      </c>
+      <c r="F74" t="s">
+        <v>42</v>
+      </c>
+      <c r="G74" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="75" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B75" t="s">
+        <v>154</v>
+      </c>
+      <c r="C75" t="s">
+        <v>168</v>
+      </c>
+      <c r="D75" t="s">
+        <v>54</v>
+      </c>
+      <c r="F75" t="s">
+        <v>35</v>
+      </c>
+      <c r="G75" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="77" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B77" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B78" t="s">
+        <v>56</v>
+      </c>
+      <c r="C78" t="s">
+        <v>57</v>
+      </c>
+      <c r="D78" t="s">
+        <v>33</v>
+      </c>
+      <c r="E78" t="s">
+        <v>34</v>
+      </c>
+      <c r="F78" t="s">
+        <v>35</v>
+      </c>
+      <c r="G78" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="79" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B79" t="s">
+        <v>56</v>
+      </c>
+      <c r="C79" t="s">
+        <v>32</v>
+      </c>
+      <c r="D79" t="s">
+        <v>33</v>
+      </c>
+      <c r="E79" t="s">
+        <v>45</v>
+      </c>
+      <c r="F79" t="s">
+        <v>35</v>
+      </c>
+      <c r="G79" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="80" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B80" t="s">
+        <v>56</v>
+      </c>
+      <c r="C80" t="s">
+        <v>59</v>
+      </c>
+      <c r="D80" t="s">
+        <v>38</v>
+      </c>
+      <c r="F80" t="s">
+        <v>35</v>
+      </c>
+      <c r="G80" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="81" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B81" t="s">
+        <v>56</v>
+      </c>
+      <c r="C81" t="s">
+        <v>61</v>
+      </c>
+      <c r="D81" t="s">
+        <v>41</v>
+      </c>
+      <c r="F81" t="s">
+        <v>35</v>
+      </c>
+      <c r="G81" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="82" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B82" t="s">
+        <v>56</v>
+      </c>
+      <c r="C82" t="s">
+        <v>176</v>
+      </c>
+      <c r="D82" t="s">
+        <v>177</v>
+      </c>
+      <c r="F82" t="s">
+        <v>35</v>
+      </c>
+      <c r="G82" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="83" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B83" t="s">
+        <v>56</v>
+      </c>
+      <c r="C83" t="s">
+        <v>179</v>
+      </c>
+      <c r="D83" t="s">
+        <v>51</v>
+      </c>
+      <c r="F83" t="s">
+        <v>35</v>
+      </c>
+      <c r="G83" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="84" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B84" t="s">
+        <v>56</v>
+      </c>
+      <c r="C84" t="s">
+        <v>181</v>
+      </c>
+      <c r="D84" t="s">
+        <v>51</v>
+      </c>
+      <c r="F84" t="s">
+        <v>35</v>
+      </c>
+      <c r="G84" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="85" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B85" t="s">
+        <v>56</v>
+      </c>
+      <c r="C85" t="s">
+        <v>183</v>
+      </c>
+      <c r="D85" t="s">
+        <v>51</v>
+      </c>
+      <c r="E85" t="s">
+        <v>45</v>
+      </c>
+      <c r="F85" t="s">
+        <v>35</v>
+      </c>
+      <c r="G85" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="86" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B86" t="s">
+        <v>56</v>
+      </c>
+      <c r="C86" t="s">
+        <v>185</v>
+      </c>
+      <c r="D86" t="s">
+        <v>114</v>
+      </c>
+      <c r="F86" t="s">
+        <v>35</v>
+      </c>
+      <c r="G86" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="87" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B87" t="s">
+        <v>56</v>
+      </c>
+      <c r="C87" t="s">
+        <v>187</v>
+      </c>
+      <c r="D87" t="s">
+        <v>51</v>
+      </c>
+      <c r="F87" t="s">
+        <v>35</v>
+      </c>
+      <c r="G87" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="88" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B88" t="s">
+        <v>56</v>
+      </c>
+      <c r="C88" t="s">
+        <v>189</v>
+      </c>
+      <c r="D88" t="s">
+        <v>114</v>
+      </c>
+      <c r="F88" t="s">
+        <v>35</v>
+      </c>
+      <c r="G88" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="89" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B89" t="s">
+        <v>56</v>
+      </c>
+      <c r="C89" t="s">
+        <v>194</v>
+      </c>
+      <c r="D89" t="s">
+        <v>33</v>
+      </c>
+      <c r="E89" t="s">
+        <v>171</v>
+      </c>
+      <c r="F89" t="s">
+        <v>200</v>
+      </c>
+      <c r="G89" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="90" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B90" t="s">
+        <v>56</v>
+      </c>
+      <c r="C90" t="s">
+        <v>50</v>
+      </c>
+      <c r="D90" t="s">
+        <v>51</v>
+      </c>
+      <c r="E90" t="s">
+        <v>45</v>
+      </c>
+      <c r="F90" t="s">
+        <v>35</v>
+      </c>
+      <c r="G90" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="91" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B91" t="s">
+        <v>56</v>
+      </c>
+      <c r="C91" t="s">
+        <v>53</v>
+      </c>
+      <c r="D91" t="s">
+        <v>54</v>
+      </c>
+      <c r="F91" t="s">
+        <v>35</v>
+      </c>
+      <c r="G91" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="92" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B92" t="s">
+        <v>56</v>
+      </c>
+      <c r="C92" t="s">
+        <v>106</v>
+      </c>
+      <c r="D92" t="s">
+        <v>51</v>
+      </c>
+      <c r="E92" t="s">
+        <v>45</v>
+      </c>
+      <c r="F92" t="s">
+        <v>42</v>
+      </c>
+      <c r="G92" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="93" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B93" t="s">
+        <v>56</v>
+      </c>
+      <c r="C93" t="s">
+        <v>92</v>
+      </c>
+      <c r="D93" t="s">
+        <v>54</v>
+      </c>
+      <c r="F93" t="s">
+        <v>42</v>
+      </c>
+      <c r="G93" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B95" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="96" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B96" t="s">
+        <v>193</v>
+      </c>
+      <c r="C96" t="s">
+        <v>194</v>
+      </c>
+      <c r="D96" t="s">
+        <v>33</v>
+      </c>
+      <c r="E96" t="s">
+        <v>34</v>
+      </c>
+      <c r="F96" t="s">
+        <v>35</v>
+      </c>
+      <c r="G96" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="97" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B97" t="s">
+        <v>193</v>
+      </c>
+      <c r="C97" t="s">
+        <v>57</v>
+      </c>
+      <c r="D97" t="s">
+        <v>33</v>
+      </c>
+      <c r="E97" t="s">
+        <v>45</v>
+      </c>
+      <c r="F97" t="s">
+        <v>35</v>
+      </c>
+      <c r="G97" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="98" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B98" t="s">
+        <v>193</v>
+      </c>
+      <c r="C98" t="s">
+        <v>197</v>
+      </c>
+      <c r="D98" t="s">
+        <v>198</v>
+      </c>
+      <c r="F98" t="s">
+        <v>35</v>
+      </c>
+      <c r="G98" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="101" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B101" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="102" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B102" t="s">
+        <v>94</v>
+      </c>
+      <c r="C102" t="s">
+        <v>95</v>
+      </c>
+      <c r="D102" t="s">
+        <v>33</v>
+      </c>
+      <c r="E102" t="s">
+        <v>34</v>
+      </c>
+      <c r="F102" t="s">
+        <v>35</v>
+      </c>
+      <c r="G102" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="103" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B103" t="s">
+        <v>94</v>
+      </c>
+      <c r="C103" t="s">
+        <v>57</v>
+      </c>
+      <c r="D103" t="s">
+        <v>33</v>
+      </c>
+      <c r="E103" t="s">
+        <v>45</v>
+      </c>
+      <c r="F103" t="s">
+        <v>35</v>
+      </c>
+      <c r="G103" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="104" spans="2:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B104" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="105" spans="2:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B105" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="106" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B106" t="s">
+        <v>94</v>
+      </c>
+      <c r="C106" t="s">
+        <v>47</v>
+      </c>
+      <c r="D106" t="s">
+        <v>48</v>
+      </c>
+      <c r="F106" t="s">
+        <v>35</v>
+      </c>
+      <c r="G106" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="107" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B107" t="s">
+        <v>94</v>
+      </c>
+      <c r="C107" t="s">
+        <v>261</v>
+      </c>
+      <c r="D107" t="s">
+        <v>117</v>
+      </c>
+      <c r="F107" t="s">
+        <v>42</v>
+      </c>
+      <c r="G107" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="108" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B108" t="s">
+        <v>94</v>
+      </c>
+      <c r="C108" t="s">
+        <v>209</v>
+      </c>
+      <c r="D108" t="s">
+        <v>210</v>
+      </c>
+      <c r="F108" t="s">
+        <v>42</v>
+      </c>
+      <c r="G108" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="109" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B109" t="s">
+        <v>94</v>
+      </c>
+      <c r="C109" t="s">
+        <v>212</v>
+      </c>
+      <c r="D109" t="s">
+        <v>213</v>
+      </c>
+      <c r="F109" t="s">
+        <v>42</v>
+      </c>
+      <c r="G109" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="110" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B110" t="s">
+        <v>94</v>
+      </c>
+      <c r="C110" t="s">
+        <v>50</v>
+      </c>
+      <c r="D110" t="s">
+        <v>51</v>
+      </c>
+      <c r="E110" t="s">
+        <v>45</v>
+      </c>
+      <c r="F110" t="s">
+        <v>35</v>
+      </c>
+      <c r="G110" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="111" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B111" t="s">
+        <v>94</v>
+      </c>
+      <c r="C111" t="s">
+        <v>53</v>
+      </c>
+      <c r="D111" t="s">
+        <v>54</v>
+      </c>
+      <c r="F111" t="s">
+        <v>35</v>
+      </c>
+      <c r="G111" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="112" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B112" t="s">
+        <v>94</v>
+      </c>
+      <c r="C112" t="s">
+        <v>106</v>
+      </c>
+      <c r="D112" t="s">
+        <v>51</v>
+      </c>
+      <c r="E112" t="s">
+        <v>45</v>
+      </c>
+      <c r="F112" t="s">
+        <v>42</v>
+      </c>
+      <c r="G112" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="113" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B113" t="s">
+        <v>94</v>
+      </c>
+      <c r="C113" t="s">
+        <v>92</v>
+      </c>
+      <c r="D113" t="s">
+        <v>54</v>
+      </c>
+      <c r="F113" t="s">
+        <v>42</v>
+      </c>
+      <c r="G113" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="114" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B114" t="s">
+        <v>94</v>
+      </c>
+      <c r="C114" t="s">
+        <v>126</v>
+      </c>
+      <c r="D114" t="s">
+        <v>217</v>
+      </c>
+      <c r="F114" t="s">
+        <v>42</v>
+      </c>
+      <c r="G114" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="117" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B117" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="118" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B118" t="s">
+        <v>219</v>
+      </c>
+      <c r="C118" t="s">
+        <v>220</v>
+      </c>
+      <c r="D118" t="s">
+        <v>33</v>
+      </c>
+      <c r="E118" t="s">
+        <v>34</v>
+      </c>
+      <c r="F118" t="s">
+        <v>35</v>
+      </c>
+      <c r="G118" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="119" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B119" t="s">
+        <v>219</v>
+      </c>
+      <c r="C119" t="s">
+        <v>95</v>
+      </c>
+      <c r="D119" t="s">
+        <v>33</v>
+      </c>
+      <c r="E119" t="s">
+        <v>45</v>
+      </c>
+      <c r="F119" t="s">
+        <v>35</v>
+      </c>
+      <c r="G119" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="120" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B120" t="s">
+        <v>219</v>
+      </c>
+      <c r="C120" t="s">
+        <v>223</v>
+      </c>
+      <c r="D120" t="s">
+        <v>38</v>
+      </c>
+      <c r="F120" t="s">
+        <v>35</v>
+      </c>
+      <c r="G120" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="121" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B121" t="s">
+        <v>219</v>
+      </c>
+      <c r="C121" t="s">
+        <v>225</v>
+      </c>
+      <c r="D121" t="s">
+        <v>117</v>
+      </c>
+      <c r="F121" t="s">
+        <v>42</v>
+      </c>
+      <c r="G121" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="122" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B122" t="s">
+        <v>219</v>
+      </c>
+      <c r="C122" t="s">
+        <v>227</v>
+      </c>
+      <c r="D122" t="s">
+        <v>89</v>
+      </c>
+      <c r="F122" t="s">
+        <v>35</v>
+      </c>
+      <c r="G122" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="123" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B123" t="s">
+        <v>219</v>
+      </c>
+      <c r="C123" t="s">
+        <v>53</v>
+      </c>
+      <c r="D123" t="s">
+        <v>54</v>
+      </c>
+      <c r="F123" t="s">
+        <v>35</v>
+      </c>
+      <c r="G123" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="124" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B124" t="s">
+        <v>219</v>
+      </c>
+      <c r="C124" t="s">
+        <v>92</v>
+      </c>
+      <c r="D124" t="s">
+        <v>54</v>
+      </c>
+      <c r="F124" t="s">
+        <v>42</v>
+      </c>
+      <c r="G124" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="127" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B127" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="128" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B128" t="s">
+        <v>229</v>
+      </c>
+      <c r="C128" t="s">
+        <v>230</v>
+      </c>
+      <c r="D128" t="s">
+        <v>33</v>
+      </c>
+      <c r="E128" t="s">
+        <v>34</v>
+      </c>
+      <c r="F128" t="s">
+        <v>35</v>
+      </c>
+      <c r="G128" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="129" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B129" t="s">
+        <v>229</v>
+      </c>
+      <c r="C129" t="s">
+        <v>220</v>
+      </c>
+      <c r="D129" t="s">
+        <v>33</v>
+      </c>
+      <c r="E129" t="s">
+        <v>45</v>
+      </c>
+      <c r="F129" t="s">
+        <v>35</v>
+      </c>
+      <c r="G129" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="130" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B130" t="s">
+        <v>229</v>
+      </c>
+      <c r="C130" t="s">
+        <v>233</v>
+      </c>
+      <c r="D130" t="s">
+        <v>117</v>
+      </c>
+      <c r="F130" t="s">
+        <v>35</v>
+      </c>
+      <c r="G130" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="131" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B131" t="s">
+        <v>229</v>
+      </c>
+      <c r="C131" t="s">
+        <v>235</v>
+      </c>
+      <c r="D131" t="s">
+        <v>210</v>
+      </c>
+      <c r="F131" t="s">
+        <v>42</v>
+      </c>
+      <c r="G131" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="132" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B132" t="s">
+        <v>229</v>
+      </c>
+      <c r="C132" t="s">
+        <v>237</v>
+      </c>
+      <c r="D132" t="s">
+        <v>86</v>
+      </c>
+      <c r="F132" t="s">
+        <v>42</v>
+      </c>
+      <c r="G132" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="133" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B133" t="s">
+        <v>229</v>
+      </c>
+      <c r="C133" t="s">
+        <v>53</v>
+      </c>
+      <c r="D133" t="s">
+        <v>54</v>
+      </c>
+      <c r="F133" t="s">
+        <v>35</v>
+      </c>
+      <c r="G133" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="134" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B134" t="s">
+        <v>229</v>
+      </c>
+      <c r="C134" t="s">
+        <v>92</v>
+      </c>
+      <c r="D134" t="s">
+        <v>54</v>
+      </c>
+      <c r="F134" t="s">
+        <v>42</v>
+      </c>
+      <c r="G134" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="137" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B137" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G137" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="138" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B138" t="s">
+        <v>239</v>
+      </c>
+      <c r="C138" t="s">
+        <v>240</v>
+      </c>
+      <c r="D138" t="s">
+        <v>33</v>
+      </c>
+      <c r="E138" t="s">
+        <v>34</v>
+      </c>
+      <c r="F138" t="s">
+        <v>35</v>
+      </c>
+      <c r="G138" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="139" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B139" t="s">
+        <v>239</v>
+      </c>
+      <c r="C139" t="s">
+        <v>95</v>
+      </c>
+      <c r="D139" t="s">
+        <v>33</v>
+      </c>
+      <c r="E139" t="s">
+        <v>45</v>
+      </c>
+      <c r="F139" t="s">
+        <v>35</v>
+      </c>
+      <c r="G139" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="140" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B140" t="s">
+        <v>239</v>
+      </c>
+      <c r="C140" t="s">
+        <v>223</v>
+      </c>
+      <c r="D140" t="s">
+        <v>38</v>
+      </c>
+      <c r="F140" t="s">
+        <v>35</v>
+      </c>
+      <c r="G140" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="141" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B141" t="s">
+        <v>239</v>
+      </c>
+      <c r="C141" t="s">
+        <v>225</v>
+      </c>
+      <c r="D141" t="s">
+        <v>117</v>
+      </c>
+      <c r="F141" t="s">
+        <v>42</v>
+      </c>
+      <c r="G141" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="142" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B142" t="s">
+        <v>239</v>
+      </c>
+      <c r="C142" t="s">
+        <v>227</v>
+      </c>
+      <c r="D142" t="s">
+        <v>89</v>
+      </c>
+      <c r="F142" t="s">
+        <v>35</v>
+      </c>
+      <c r="G142" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="143" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B143" t="s">
+        <v>239</v>
+      </c>
+      <c r="C143" t="s">
+        <v>53</v>
+      </c>
+      <c r="D143" t="s">
+        <v>54</v>
+      </c>
+      <c r="F143" t="s">
+        <v>35</v>
+      </c>
+      <c r="G143" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="144" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B144" t="s">
+        <v>239</v>
+      </c>
+      <c r="C144" t="s">
+        <v>92</v>
+      </c>
+      <c r="D144" t="s">
+        <v>54</v>
+      </c>
+      <c r="F144" t="s">
+        <v>42</v>
+      </c>
+      <c r="G144" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="147" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B147" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G147" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="148" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B148" t="s">
+        <v>245</v>
+      </c>
+      <c r="C148" t="s">
+        <v>246</v>
+      </c>
+      <c r="D148" t="s">
+        <v>33</v>
+      </c>
+      <c r="E148" t="s">
+        <v>34</v>
+      </c>
+      <c r="F148" t="s">
+        <v>35</v>
+      </c>
+      <c r="G148" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="149" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B149" t="s">
+        <v>245</v>
+      </c>
+      <c r="C149" t="s">
+        <v>95</v>
+      </c>
+      <c r="D149" t="s">
+        <v>33</v>
+      </c>
+      <c r="E149" t="s">
+        <v>45</v>
+      </c>
+      <c r="F149" t="s">
+        <v>35</v>
+      </c>
+      <c r="G149" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="150" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B150" t="s">
+        <v>245</v>
+      </c>
+      <c r="C150" t="s">
+        <v>98</v>
+      </c>
+      <c r="D150" t="s">
+        <v>117</v>
+      </c>
+      <c r="F150" t="s">
+        <v>35</v>
+      </c>
+      <c r="G150" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="151" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B151" t="s">
+        <v>245</v>
+      </c>
+      <c r="C151" t="s">
+        <v>250</v>
+      </c>
+      <c r="D151" t="s">
+        <v>217</v>
+      </c>
+      <c r="F151" t="s">
+        <v>42</v>
+      </c>
+      <c r="G151" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="152" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B152" t="s">
+        <v>245</v>
+      </c>
+      <c r="C152" t="s">
+        <v>252</v>
+      </c>
+      <c r="D152" t="s">
+        <v>51</v>
+      </c>
+      <c r="E152" t="s">
+        <v>45</v>
+      </c>
+      <c r="F152" t="s">
+        <v>35</v>
+      </c>
+      <c r="G152" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="153" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B153" t="s">
+        <v>245</v>
+      </c>
+      <c r="C153" t="s">
+        <v>254</v>
+      </c>
+      <c r="D153" t="s">
+        <v>54</v>
+      </c>
+      <c r="F153" t="s">
+        <v>35</v>
+      </c>
+      <c r="G153" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="156" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B156" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G156" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="157" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B157" t="s">
+        <v>256</v>
+      </c>
+      <c r="C157" t="s">
+        <v>257</v>
+      </c>
+      <c r="D157" t="s">
+        <v>33</v>
+      </c>
+      <c r="E157" t="s">
+        <v>34</v>
+      </c>
+      <c r="F157" t="s">
+        <v>35</v>
+      </c>
+      <c r="G157" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="158" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B158" t="s">
+        <v>256</v>
+      </c>
+      <c r="C158" t="s">
+        <v>240</v>
+      </c>
+      <c r="D158" t="s">
+        <v>33</v>
+      </c>
+      <c r="E158" t="s">
+        <v>45</v>
+      </c>
+      <c r="F158" t="s">
+        <v>35</v>
+      </c>
+      <c r="G158" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="159" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B159" t="s">
+        <v>256</v>
+      </c>
+      <c r="C159" t="s">
+        <v>233</v>
+      </c>
+      <c r="D159" t="s">
+        <v>117</v>
+      </c>
+      <c r="F159" t="s">
+        <v>35</v>
+      </c>
+      <c r="G159" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="160" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B160" t="s">
+        <v>256</v>
+      </c>
+      <c r="C160" t="s">
+        <v>235</v>
+      </c>
+      <c r="D160" t="s">
+        <v>210</v>
+      </c>
+      <c r="F160" t="s">
+        <v>42</v>
+      </c>
+      <c r="G160" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="161" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B161" t="s">
+        <v>256</v>
+      </c>
+      <c r="C161" t="s">
+        <v>237</v>
+      </c>
+      <c r="D161" t="s">
+        <v>86</v>
+      </c>
+      <c r="F161" t="s">
+        <v>42</v>
+      </c>
+      <c r="G161" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="162" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B162" t="s">
+        <v>256</v>
+      </c>
+      <c r="C162" t="s">
+        <v>53</v>
+      </c>
+      <c r="D162" t="s">
+        <v>54</v>
+      </c>
+      <c r="F162" t="s">
+        <v>35</v>
+      </c>
+      <c r="G162" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="163" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B163" t="s">
+        <v>256</v>
+      </c>
+      <c r="C163" t="s">
+        <v>92</v>
+      </c>
+      <c r="D163" t="s">
+        <v>54</v>
+      </c>
+      <c r="F163" t="s">
+        <v>42</v>
+      </c>
+      <c r="G163" t="s">
+        <v>93</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>